--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.0.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2146,7 +2146,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:02:16+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2163,14 +2163,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx       — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx   — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_COMPSETS.xlsx   — compset (peer-set) benchmarks per target hotel</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
         </is>
       </c>
     </row>
@@ -2194,147 +2194,164 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operating contract:</t>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     in ingested_by + notes.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sheets:</t>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • README            — this sheet</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reference docs:</t>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-submarket-schema.md</t>
+          <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-submarket-schema.md</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Regenerating this workbook:</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regenerating this workbook:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -441,12 +441,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:AO11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -455,7 +455,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -463,21 +463,21 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="24" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="18" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="31" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="19" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
@@ -693,6 +693,1076 @@
           <t>notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Madrid Centre</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>233.2521</v>
+      </c>
+      <c r="N2" t="n">
+        <v>184.0215</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>16954</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>396</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Madrid Centre</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chamartin &amp; Plaza de Castilla</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="M3" t="n">
+        <v>147.9022</v>
+      </c>
+      <c r="N3" t="n">
+        <v>109.9747</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.180000000000001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6322</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>144</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Chamartin &amp; Plaza de Castilla</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="M4" t="n">
+        <v>247.8348</v>
+      </c>
+      <c r="N4" t="n">
+        <v>183.8536</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5291</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>113</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arguelles &amp; Chamberi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>71.39999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>185.9745</v>
+      </c>
+      <c r="N5" t="n">
+        <v>132.785</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4419</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Arguelles &amp; Chamberi</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>75.03</v>
+      </c>
+      <c r="M6" t="n">
+        <v>250.5235</v>
+      </c>
+      <c r="N6" t="n">
+        <v>187.9582</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1442</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Castille-Leon/CLM/Extremadura ESP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Castille &amp; Leon Regional</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>67.67999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>89.6146</v>
+      </c>
+      <c r="N7" t="n">
+        <v>60.6496</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.959999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>24557</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>192</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Castille &amp; Leon Regional</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Castille-Leon/CLM/Extremadura ESP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha Regional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="M8" t="n">
+        <v>79.5595</v>
+      </c>
+      <c r="N8" t="n">
+        <v>51.6914</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>11332</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>122</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Castilla-La Mancha Regional</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Barajas/Hortaleza/San Blas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>112.6226</v>
+      </c>
+      <c r="N9" t="n">
+        <v>86.1349</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.130000000000001</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9611</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Barajas/Hortaleza/San Blas</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Madrid Province Regional</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>73.61999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>84.87269999999999</v>
+      </c>
+      <c r="N10" t="n">
+        <v>62.4841</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8389</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Madrid Province Regional</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Madrid ESP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Madrid Surrounding</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ltm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="M11" t="n">
+        <v>110.8054</v>
+      </c>
+      <c r="N11" t="n">
+        <v>83.5748</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8351</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>503</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Madrid Surrounding</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>batch_04ef5ec3e6b54457</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>snapshot.json</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>costar</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026-05-14T02:33:19+00:00</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>cli:build_masters</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>ingested</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1683,7 +2753,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2120,7 +3190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2146,7 +3216,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
+          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2163,195 +3233,202 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx                  — country aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx              — market aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx — submarket aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_SUBMERCADOS.xlsx           — submarket aggregates (Dataset A)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_HOTELES_POR_MERCADO.xlsx   — hotel inventory (Dataset B · v1.2)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx                 — LEGACY (chain-scale aggregates · retired v1.2)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Operating contract:</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sheets:</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Reference docs:</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-submarket-schema.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-submarket-schema.md</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Regenerating this workbook:</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+          <t>Regenerating this workbook:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -773,7 +773,7 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -880,7 +880,7 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1415,7 +1415,7 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1629,7 +1629,7 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1736,7 +1736,7 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -3216,7 +3216,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,20 +471,22 @@
     <col width="18" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="17" customWidth="1" min="27" max="27"/>
-    <col width="31" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="15" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="31" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="27" customWidth="1" min="35" max="35"/>
+    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="23" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="17" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
-    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,70 +627,80 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>rooms_under_construction</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rooms_delivered_12m</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>canonical_id</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ingestion_id</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>source_kind</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ingested_at</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ingested_by</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>normalization_version</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>dedup_key</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>review_required</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>review_reason</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ingestion_status</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>supersedes_id</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -750,56 +762,62 @@
       <c r="Z2" t="n">
         <v>396</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>396</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Madrid Centre</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -857,56 +875,62 @@
       <c r="Z3" t="n">
         <v>144</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" t="n">
+        <v>144</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Chamartin &amp; Plaza de Castilla</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -964,56 +988,62 @@
       <c r="Z4" t="n">
         <v>113</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" t="n">
+        <v>113</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Salamanca</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1071,56 +1101,62 @@
       <c r="Z5" t="n">
         <v>17</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Arguelles &amp; Chamberi</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1178,56 +1214,62 @@
       <c r="Z6" t="n">
         <v>61</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB6" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Retiro</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1285,56 +1327,62 @@
       <c r="Z7" t="n">
         <v>192</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB7" t="n">
+        <v>192</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>67</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Castille &amp; Leon Regional</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1392,56 +1440,62 @@
       <c r="Z8" t="n">
         <v>122</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB8" t="n">
+        <v>122</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Castilla-La Mancha Regional</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1499,56 +1553,62 @@
       <c r="Z9" t="n">
         <v>881</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB9" t="n">
+        <v>881</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>647</v>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Barajas/Hortaleza/San Blas</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1606,56 +1666,62 @@
       <c r="Z10" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Madrid Province Regional</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1713,56 +1779,62 @@
       <c r="Z11" t="n">
         <v>503</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB11" t="n">
+        <v>503</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>125</v>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Madrid Surrounding</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>batch_976be391c94a4aae</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>batch_43847c5c0d554445</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>snapshot.json</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>costar</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2026-05-14T02:59:23+00:00</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2026-05-14T03:06:34+00:00</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>cli:build_masters</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>v1.4</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr">
+        <is>
           <t>ingested</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1775,11 +1847,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
@@ -2544,54 +2616,54 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ingestion_meta</t>
+          <t>domain</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>canonical_id</t>
+          <t>rooms_under_construction</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Primary key in the master. Generated on first insertion. Stable across edits.</t>
+          <t>Rooms under construction — 'Habitaciones construcción'.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ingestion_meta</t>
+          <t>domain</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ingestion_id</t>
+          <t>rooms_delivered_12m</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Matches the ingestion log entry that landed this row.</t>
+          <t>Rooms delivered last 12m — 'Habitaciones entregadas 12 m.'.</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2675,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>source_file</t>
+          <t>canonical_id</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2618,7 +2690,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Original filename verbatim — e.g. 'CoStar_ES_Country_2026Q1.xlsx'.</t>
+          <t>Primary key in the master. Generated on first insertion. Stable across edits.</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2702,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>source_kind</t>
+          <t>ingestion_id</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2645,7 +2717,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>costar | str | kalibri | curated | manual</t>
+          <t>Matches the ingestion log entry that landed this row.</t>
         </is>
       </c>
     </row>
@@ -2657,22 +2729,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>source_file</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Public URL when applicable.</t>
+          <t>Original filename verbatim — e.g. 'CoStar_ES_Country_2026Q1.xlsx'.</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2756,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ingested_at</t>
+          <t>source_kind</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2699,7 +2771,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ISO-8601 UTC. Auto-stamped by the ingestion run.</t>
+          <t>costar | str | kalibri | curated | manual</t>
         </is>
       </c>
     </row>
@@ -2711,22 +2783,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ingested_by</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Operator email — audit trail.</t>
+          <t>Public URL when applicable.</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2810,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>normalization_version</t>
+          <t>ingested_at</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2753,7 +2825,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
+          <t>ISO-8601 UTC. Auto-stamped by the ingestion run.</t>
         </is>
       </c>
     </row>
@@ -2765,12 +2837,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>dedup_key</t>
+          <t>ingested_by</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2780,7 +2852,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>sha256 of the canonicalised dedup fields (see costar-normalization-rules.md §4).</t>
+          <t>Operator email — audit trail.</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2864,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>normalization_version</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2807,7 +2879,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TRUE when validation flagged something.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.2.</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2891,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>review_reason</t>
+          <t>dedup_key</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2829,12 +2901,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Short label — e.g. 'missing_period', 'duplicate_candidate', 'fx_conversion_applied'.</t>
+          <t>sha256 of the canonicalised dedup fields (see costar-normalization-rules.md §4).</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2918,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ingestion_status</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2861,7 +2933,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ingested | under_review | superseded | rejected</t>
+          <t>TRUE when validation flagged something.</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2945,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>supersedes_id</t>
+          <t>review_reason</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2888,7 +2960,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Set when this row corrects/replaces a previously canonical row.</t>
+          <t>Short label — e.g. 'missing_period', 'duplicate_candidate', 'fx_conversion_applied'.</t>
         </is>
       </c>
     </row>
@@ -2900,20 +2972,74 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>ingestion_status</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ingested | under_review | superseded | rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ingestion_meta</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>supersedes_id</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Set when this row corrects/replaces a previously canonical row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ingestion_meta</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Free-form operator notes.</t>
         </is>
@@ -3216,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>batch_0c2ed97284e04906</t>
+          <t>batch_e42e7d8a74164197</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:16:15+00:00</t>
+          <t>2026-05-14T03:22:23+00:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>batch_e42e7d8a74164197</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:22:23+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:23:25+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_SUBMERCADOS.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -791,7 +791,7 @@
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -904,7 +904,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1582,7 +1582,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1808,7 +1808,7 @@
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3342,7 +3342,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:48:39+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
